--- a/output/pdf_financials_xlsx/PGLD.xlsx
+++ b/output/pdf_financials_xlsx/PGLD.xlsx
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.239738</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.406663</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -6961,7 +6961,11 @@
           <t>Warrant reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7010,7 +7014,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -7373,7 +7381,11 @@
           <t>Warrant reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -7424,7 +7436,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PGLD.xlsx
+++ b/output/pdf_financials_xlsx/PGLD.xlsx
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009727</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.020883</v>
@@ -1223,7 +1223,7 @@
         <v>-0.904336</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.304631</v>
+        <v>-1.294904</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-12.959203</v>
@@ -1283,7 +1283,7 @@
         <v>-0.904336</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.2567</v>
+        <v>-1.246973</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-12.808263</v>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.499977</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.068312</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.570337</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.474424</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.499977</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.068312</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.570337</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.474424</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.499977</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.157417</v>
+        <v>0.089105</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.620245</v>
+        <v>0.049908</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.686928</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052219</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052219</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -12258,7 +12258,11 @@
           <t>Lease payments (Note 11)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -15642,7 +15646,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -15954,7 +15958,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">

--- a/output/pdf_financials_xlsx/PGLD.xlsx
+++ b/output/pdf_financials_xlsx/PGLD.xlsx
@@ -522,10 +522,8 @@
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -552,10 +550,8 @@
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +578,8 @@
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -610,12 +604,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.536795</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.555252</v>
       </c>
     </row>
     <row r="8">
@@ -642,10 +634,8 @@
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -672,10 +662,8 @@
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -700,12 +688,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.536795</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.555252</v>
       </c>
     </row>
     <row r="11">
@@ -732,10 +718,8 @@
       <c r="G11" s="3" t="n">
         <v>-2.104891</v>
       </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H11" s="3" t="n">
+        <v>-4.968436</v>
       </c>
     </row>
     <row r="12">
@@ -762,10 +746,8 @@
       <c r="G12" s="3" t="n">
         <v>0.003901</v>
       </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H12" s="3" t="n">
+        <v>0.091886</v>
       </c>
     </row>
     <row r="13">
@@ -792,10 +774,8 @@
       <c r="G13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -822,10 +802,8 @@
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -852,10 +830,8 @@
       <c r="G15" s="3" t="n">
         <v>-0.069205</v>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H15" s="3" t="n">
+        <v>-0.006424</v>
       </c>
     </row>
     <row r="16">
@@ -880,12 +856,10 @@
         <v>-4.482038</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.148527</v>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.14855</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-10.093981</v>
       </c>
     </row>
     <row r="17">
@@ -910,12 +884,10 @@
         <v>0.025166</v>
       </c>
       <c r="G17" s="3" t="n">
+        <v>-2.3e-05</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1026,10 +998,8 @@
       <c r="G20" s="3" t="n">
         <v>4.148527</v>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="3" t="n">
+        <v>-10.093981</v>
       </c>
     </row>
     <row r="21">
@@ -1056,10 +1026,8 @@
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1086,10 +1054,8 @@
       <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1144,10 +1110,8 @@
       <c r="G24" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H24" s="3" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="25">
@@ -1174,10 +1138,8 @@
       <c r="G25" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H25" s="3" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="26">
@@ -1204,10 +1166,8 @@
       <c r="G26" s="3" t="n">
         <v>144.907673</v>
       </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H26" s="3" t="n">
+        <v>170.167064</v>
       </c>
     </row>
     <row r="27">
@@ -1232,12 +1192,10 @@
         <v>-4.489887</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.144626</v>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.144649</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-10.185867</v>
       </c>
     </row>
     <row r="28">
@@ -1264,10 +1222,8 @@
       <c r="G28" s="3" t="n">
         <v>0.036246</v>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H28" s="3" t="n">
+        <v>0.024161</v>
       </c>
     </row>
     <row r="29">
@@ -1292,12 +1248,10 @@
         <v>-4.326353</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.180872</v>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.180895</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-10.161706</v>
       </c>
     </row>
     <row r="30">
@@ -1364,12 +1318,10 @@
         <v>-0.5614856455924738</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0005544105771896205</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1605,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.009174</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.015223</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0.097815</v>
@@ -1633,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.009174</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.015223</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.097815</v>
@@ -1829,10 +1781,10 @@
         <v>0.049908</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.686928</v>
+        <v>0.677754</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.167554</v>
+        <v>0.152331</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2298,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.302253</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.045627</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -2379,16 +2331,16 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.030344</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.057732</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="68">
@@ -2463,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.133446</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2472,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.001951</v>
       </c>
     </row>
     <row r="71">
@@ -2491,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.133446</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -2500,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.001951</v>
       </c>
     </row>
     <row r="72">
@@ -2603,7 +2555,7 @@
         <v>0.040532</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>11.855199</v>
+        <v>11.721753</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>5.102915</v>
@@ -2612,7 +2564,7 @@
         <v>2.544051</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>8.042726</v>
+        <v>8.040775</v>
       </c>
     </row>
     <row r="76">
@@ -2696,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>0.000176</v>
       </c>
     </row>
     <row r="79">
@@ -2724,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>0.000176</v>
       </c>
     </row>
     <row r="80">
@@ -2746,10 +2698,8 @@
       <c r="D80" s="3" t="n">
         <v>0.01078370807253117</v>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>-0.01356925944398433</v>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
@@ -2761,10 +2711,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.0009329638907445332</v>
       </c>
     </row>
     <row r="81">
@@ -2904,7 +2852,7 @@
         <v>2.894028</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>8.848214</v>
+        <v>8.848038000000001</v>
       </c>
     </row>
     <row r="86">
@@ -4345,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:K266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4780,7 +4728,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5023,7 +4975,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7593,7 +7549,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -9479,7 +9439,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -10436,7 +10400,11 @@
           <t>Proceeds from FTS private placement 13</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -11346,7 +11314,11 @@
           <t>Proceeds from FTS private placement 14</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -13351,10 +13323,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>control that we identify during our audit.</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Exploration and evaluation ("E&amp;E") expenditures 11 $</t>
+          <t>Exploration and evaluation ("E&amp;E") expenditures 13 $</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13378,16 +13354,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n">
-        <v>4.434049</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J178" s="5" t="n">
         <v>0.434712</v>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K178" s="5" t="n">
+        <v>3.043848</v>
       </c>
     </row>
     <row r="179">
@@ -13403,14 +13379,10 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation 16</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -13426,19 +13398,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" s="5" t="n">
-        <v>0.89302</v>
-      </c>
-      <c r="I179" s="5" t="n">
-        <v>0.672463</v>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J179" s="5" t="n">
-        <v>0.536795</v>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.174409</v>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>0.781464</v>
       </c>
     </row>
     <row r="180">
@@ -13454,10 +13428,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Investor relations and travel</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Office and general 14</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -13473,19 +13451,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="5" t="n">
-        <v>0.458833</v>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>0.769888</v>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J180" s="5" t="n">
-        <v>0.535595</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.536795</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>0.555252</v>
       </c>
     </row>
     <row r="181">
@@ -13501,14 +13481,10 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Investor relations and travel</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -13525,18 +13501,16 @@
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>0.220454</v>
+        <v>0.458833</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>0.381521</v>
+        <v>0.769888</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>0.287794</v>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.535595</v>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0.302385</v>
       </c>
     </row>
     <row r="182">
@@ -13552,10 +13526,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Share-based compensation 13</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -13571,21 +13549,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H182" s="5" t="n">
+        <v>0.220454</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.488334</v>
+        <v>0.381521</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.174409</v>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.287794</v>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>0.15823</v>
       </c>
     </row>
     <row r="183">
@@ -13629,10 +13603,8 @@
       <c r="J183" s="5" t="n">
         <v>0.09934</v>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K183" s="5" t="n">
+        <v>0.103096</v>
       </c>
     </row>
     <row r="184">
@@ -13648,7 +13620,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
+          <t>Depreciation 8</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13671,10 +13643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H184" s="5" t="n">
+        <v>0.15094</v>
       </c>
       <c r="I184" s="5" t="n">
         <v>0.163534</v>
@@ -13682,10 +13652,8 @@
       <c r="J184" s="5" t="n">
         <v>0.036246</v>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K184" s="5" t="n">
+        <v>0.024161</v>
       </c>
     </row>
     <row r="185">
@@ -13733,10 +13701,8 @@
       <c r="J185" s="5" t="n">
         <v>1.670179</v>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K185" s="5" t="n">
+        <v>1.924588</v>
       </c>
     </row>
     <row r="186">
@@ -13784,10 +13750,8 @@
       <c r="J186" s="5" t="n">
         <v>-2.104891</v>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K186" s="5" t="n">
+        <v>-4.968436</v>
       </c>
     </row>
     <row r="187">
@@ -13803,7 +13767,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Interest and finance expense 12</t>
+          <t>(Loss) gain on financial instruments at fair value 11 , 12</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13827,16 +13791,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I187" s="5" t="n">
-        <v>-1.078274</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J187" s="5" t="n">
-        <v>-0.470388</v>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.149679</v>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>-6.485218</v>
       </c>
     </row>
     <row r="188">
@@ -13852,14 +13816,10 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest and finance expense 15</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -13880,16 +13840,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I188" s="5" t="n">
-        <v>0.128262</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J188" s="5" t="n">
-        <v>-0.08942600000000001</v>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.470388</v>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>-0.115964</v>
       </c>
     </row>
     <row r="189">
@@ -13905,10 +13865,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Loss on sale of property, plant and equipment 7</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -13935,12 +13899,10 @@
         </is>
       </c>
       <c r="J189" s="5" t="n">
-        <v>-0.01496</v>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.08942600000000001</v>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>-0.006462</v>
       </c>
     </row>
     <row r="190">
@@ -13956,14 +13918,10 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Interest and finance income</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Loss on sale of property, plant and equipment 8</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -13979,14 +13937,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>0.020883</v>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>0.007849</v>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J190" s="5" t="n">
-        <v>0.003901</v>
+        <v>-0.01496</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14007,14 +13969,10 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on extinguishment of related party loans 16 , 17</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -14041,7 +13999,7 @@
         </is>
       </c>
       <c r="J191" s="5" t="n">
-        <v>0.020221</v>
+        <v>0.1145</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14062,10 +14020,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Other income - sale of mineral claims 11</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -14092,12 +14054,10 @@
         </is>
       </c>
       <c r="J192" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020221</v>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>3.8e-05</v>
       </c>
     </row>
     <row r="193">
@@ -14113,7 +14073,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of related party loans 13 , 14</t>
+          <t>Realized gain on sale of marketable securities 6</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14142,13 +14102,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J193" s="5" t="n">
-        <v>0.1145</v>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>0.010685</v>
       </c>
     </row>
     <row r="194">
@@ -14164,7 +14124,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Gain on financial instruments at fair value 9 , 10</t>
+          <t>Gain on extinguishment of acquisition liabilities 11</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -14188,16 +14148,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I194" s="5" t="n">
-        <v>1.102568</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J194" s="5" t="n">
-        <v>0.149679</v>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.360508</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>0.011706</v>
       </c>
     </row>
     <row r="195">
@@ -14213,10 +14173,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of acquisition liabilities 9</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Interest and finance income</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -14232,21 +14196,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H195" s="5" t="n">
+        <v>0.020883</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>2.056201</v>
+        <v>0.007849</v>
       </c>
       <c r="J195" s="5" t="n">
-        <v>6.360508</v>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003901</v>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>0.091886</v>
       </c>
     </row>
     <row r="196">
@@ -14262,7 +14222,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Earnings (loss) before taxes</t>
+          <t>Unrealized fair value gain on marketable securities 6</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -14286,16 +14246,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I196" s="5" t="n">
-        <v>-4.792243</v>
-      </c>
-      <c r="J196" s="5" t="n">
-        <v>4.019144</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>0.167784</v>
       </c>
     </row>
     <row r="197">
@@ -14311,7 +14273,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Current income tax recovery (expense) 16</t>
+          <t>Other income - sale of mineral claims 13</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -14335,16 +14297,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I197" s="5" t="n">
-        <v>-0.025166</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J197" s="5" t="n">
-        <v>2.3e-05</v>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="198">
@@ -14360,7 +14322,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 16</t>
+          <t>Earnings (loss) before taxes</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -14384,18 +14346,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I198" s="5" t="n">
+        <v>-4.792243</v>
       </c>
       <c r="J198" s="5" t="n">
-        <v>0.12936</v>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.019144</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>-10.093981</v>
       </c>
     </row>
     <row r="199">
@@ -14411,10 +14369,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Flow-through share ("FTS") premium recovery 16</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Current income tax recovery 19</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -14435,13 +14397,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I199" s="5" t="n">
-        <v>0.360537</v>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>2.3e-05</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14462,12 +14424,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Net earnings (loss) for the year $</t>
+          <t>Deferred income tax recovery 19</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -14490,11 +14452,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I200" s="5" t="n">
-        <v>-4.456872</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J200" s="5" t="n">
-        <v>4.148527</v>
+        <v>0.12936</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -14510,15 +14474,19 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings (loss), net of tax</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Currency translation adjustments</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Net earnings (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -14540,15 +14508,13 @@
         </is>
       </c>
       <c r="I201" s="5" t="n">
-        <v>-0.015101</v>
+        <v>-4.456872</v>
       </c>
       <c r="J201" s="5" t="n">
-        <v>-0.137778</v>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.148527</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>-10.093981</v>
       </c>
     </row>
     <row r="202">
@@ -14559,12 +14525,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>financial instruments designated at fair value through</t>
+          <t>Other comprehensive earnings (loss), net of tax</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>financial instruments designated at fair value through profit or loss ("FVTPL")</t>
+          <t>Currency translation adjustments</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -14588,18 +14554,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I202" s="5" t="n">
+        <v>-0.015101</v>
       </c>
       <c r="J202" s="5" t="n">
-        <v>-0.002243</v>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.137778</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.008163999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -14615,14 +14577,10 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Comprehensive earnings (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>financial instruments designated at fair value through profit or loss ("FVTPL")</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -14643,11 +14601,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I203" s="5" t="n">
-        <v>-4.471973</v>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J203" s="5" t="n">
-        <v>4.008506</v>
+        <v>-0.002243</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -14663,17 +14623,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share</t>
+          <t>financial instruments designated at fair value through</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Comprehensive earnings (loss) for the year $</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -14697,15 +14657,13 @@
         </is>
       </c>
       <c r="I204" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-4.471973</v>
       </c>
       <c r="J204" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.008506</v>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>-10.085817</v>
       </c>
     </row>
     <row r="205">
@@ -14721,12 +14679,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Diluted 13 $</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -14755,10 +14713,8 @@
       <c r="J205" s="5" t="n">
         <v>3e-08</v>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K205" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="206">
@@ -14769,17 +14725,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earnings (loss) per share</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Diluted 16 $</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -14802,16 +14758,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I206" s="5" t="n">
-        <v>101.447812</v>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J206" s="5" t="n">
-        <v>124.864438</v>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="207">
@@ -14822,17 +14778,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Diluted 13</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -14855,16 +14811,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" s="5" t="n">
-        <v>101.447812</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J207" s="5" t="n">
-        <v>144.907673</v>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>124.864438</v>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>170.167064</v>
       </c>
     </row>
     <row r="208">
@@ -14873,13 +14829,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Exploration and evaluation ("E&amp;E") expenditures 12 $</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Diluted 16</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -14895,21 +14859,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H208" s="5" t="n">
-        <v>11.410978</v>
-      </c>
-      <c r="I208" s="5" t="n">
-        <v>4.434049</v>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="n">
+        <v>144.907673</v>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>170.167064</v>
       </c>
     </row>
     <row r="209">
@@ -14918,14 +14882,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Administrative expenses</t>
-        </is>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Share-based compensation 14</t>
+          <t>Exploration and evaluation ("E&amp;E") expenditures 11 $</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -14944,16 +14904,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" s="5" t="n">
-        <v>1.334591</v>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I209" s="5" t="n">
-        <v>0.488334</v>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.434049</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>0.434712</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -14974,12 +14934,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -14998,15 +14958,13 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.15094</v>
+        <v>0.89302</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>0.163534</v>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.672463</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>0.536795</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15027,7 +14985,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Interest and finance expense 13</t>
+          <t>Share-based compensation 13</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -15046,16 +15004,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" s="5" t="n">
-        <v>-1.057811</v>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I211" s="5" t="n">
-        <v>-1.078274</v>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.488334</v>
+      </c>
+      <c r="J211" s="5" t="n">
+        <v>0.174409</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15076,12 +15034,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Depreciation 7</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -15099,16 +15057,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H212" s="5" t="n">
-        <v>-0.001674</v>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I212" s="5" t="n">
-        <v>0.128262</v>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.163534</v>
+      </c>
+      <c r="J212" s="5" t="n">
+        <v>0.036246</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -15129,7 +15087,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Gain on financial instruments at fair value 11</t>
+          <t>Interest and finance expense 12</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -15154,12 +15112,10 @@
         </is>
       </c>
       <c r="I213" s="5" t="n">
-        <v>1.102568</v>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.078274</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>-0.470388</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -15180,10 +15136,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gain on modification/extinguishment of acquisition liabilities 11</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
+          <t>Foreign exchange (loss) gain</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -15199,16 +15159,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H214" s="5" t="n">
-        <v>0.729012</v>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I214" s="5" t="n">
-        <v>2.056201</v>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.128262</v>
+      </c>
+      <c r="J214" s="5" t="n">
+        <v>-0.08942600000000001</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -15229,7 +15189,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Loss before taxes</t>
+          <t>Loss on sale of property, plant and equipment 7</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -15248,16 +15208,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" s="5" t="n">
-        <v>-14.899878</v>
-      </c>
-      <c r="I215" s="5" t="n">
-        <v>-4.792243</v>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>-0.01496</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -15278,14 +15240,10 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Current income tax expense 17</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Other income - sale of mineral claims 11</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -15301,16 +15259,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" s="5" t="n">
-        <v>-0.000199</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>-0.025166</v>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -15331,7 +15291,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FTS premium recovery 17</t>
+          <t>Gain on extinguishment of related party loans 13 , 14</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -15350,16 +15310,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" s="5" t="n">
-        <v>1.961956</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>0.360537</v>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" s="5" t="n">
+        <v>0.1145</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -15380,14 +15342,10 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on financial instruments at fair value 9 , 10</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -15403,16 +15361,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H218" s="5" t="n">
-        <v>-12.938121</v>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I218" s="5" t="n">
-        <v>-4.456872</v>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.102568</v>
+      </c>
+      <c r="J218" s="5" t="n">
+        <v>0.149679</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -15428,12 +15386,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Other comprehensive loss, net of tax</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Currency translation adjustments</t>
+          <t>Gain on extinguishment of acquisition liabilities 9</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -15452,16 +15410,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" s="5" t="n">
-        <v>-0.676871</v>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I219" s="5" t="n">
-        <v>-0.015101</v>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.056201</v>
+      </c>
+      <c r="J219" s="5" t="n">
+        <v>6.360508</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -15477,17 +15435,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Other comprehensive loss, net of tax</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Current income tax recovery (expense) 16</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -15505,16 +15463,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" s="5" t="n">
-        <v>-13.614992</v>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I220" s="5" t="n">
-        <v>-4.471973</v>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025166</v>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>2.3e-05</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -15530,17 +15488,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Other comprehensive loss, net of tax</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Deferred income tax recovery 16</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -15558,16 +15516,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>-1.7e-07</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>0.12936</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -15583,19 +15543,15 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Other comprehensive loss, net of tax</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Flow-through share ("FTS") premium recovery 16</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -15611,11 +15567,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" s="5" t="n">
-        <v>76.123304</v>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I222" s="5" t="n">
-        <v>101.447812</v>
+        <v>0.360537</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -15636,17 +15594,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Earnings (loss) per share</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Diluted 13 $</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -15659,23 +15617,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G223" s="5" t="n">
-        <v>-0.009727</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I223" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="J223" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -15691,42 +15647,44 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E224" s="5" t="n">
-        <v>0.1065</v>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>0.327995</v>
-      </c>
-      <c r="G224" s="5" t="n">
-        <v>0.303614</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I224" s="5" t="n">
+        <v>101.447812</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>124.864438</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -15742,42 +15700,44 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Diluted 13</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="F225" s="5" t="n">
-        <v>0.080274</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>0.072243</v>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I225" s="5" t="n">
+        <v>101.447812</v>
+      </c>
+      <c r="J225" s="5" t="n">
+        <v>144.907673</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -15791,21 +15751,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Administrative Expenses</t>
-        </is>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Depreciation (Note 9)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation ("E&amp;E") expenditures 12 $</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -15816,18 +15768,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G226" s="5" t="n">
-        <v>0.047931</v>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>11.410978</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>4.434049</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -15848,12 +15798,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Part XII.6 tax</t>
+          <t>Share-based compensation 14</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -15867,18 +15817,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G227" s="5" t="n">
-        <v>0.004364</v>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>1.334591</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>0.488334</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -15899,12 +15847,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 14)</t>
+          <t>Interest and finance expense 13</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -15913,21 +15861,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F228" s="5" t="n">
-        <v>0.112776</v>
-      </c>
-      <c r="G228" s="5" t="n">
-        <v>0.16208</v>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>-1.057811</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>-1.078274</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -15948,17 +15896,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Interest expense (Note 11)</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -15971,18 +15919,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G229" s="5" t="n">
-        <v>0.006181</v>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>-0.001674</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>0.128262</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -16003,20 +15949,24 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Interest on related party loans</t>
+          <t>Gain on financial instruments at fair value 11</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" s="5" t="n">
-        <v>0.002973</v>
-      </c>
-      <c r="F230" s="5" t="n">
-        <v>0.005466</v>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -16028,10 +15978,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I230" s="5" t="n">
+        <v>1.102568</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -16052,12 +16000,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Shareholder information</t>
+          <t>Gain on modification/extinguishment of acquisition liabilities 11</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -16066,21 +16014,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F231" s="5" t="n">
-        <v>0.07061000000000001</v>
-      </c>
-      <c r="G231" s="5" t="n">
-        <v>0.04427</v>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>0.729012</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>2.056201</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -16101,12 +16049,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Investor relations and travel</t>
+          <t>Loss before taxes</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -16115,21 +16063,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F232" s="5" t="n">
-        <v>0.024584</v>
-      </c>
-      <c r="G232" s="5" t="n">
-        <v>0.083657</v>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>-14.899878</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>-4.792243</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -16150,37 +16098,39 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Total Administrative Expenses</t>
+          <t>Current income tax expense 17</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E233" s="5" t="n">
-        <v>-0.110996</v>
-      </c>
-      <c r="F233" s="5" t="n">
-        <v>-0.621705</v>
-      </c>
-      <c r="G233" s="5" t="n">
-        <v>-0.7146130000000001</v>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>-0.000199</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>-0.025166</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -16201,33 +16151,35 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 4)</t>
+          <t>FTS premium recovery 17</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
-      <c r="E234" s="5" t="n">
-        <v>-0.364586</v>
-      </c>
-      <c r="F234" s="5" t="n">
-        <v>-0.496069</v>
-      </c>
-      <c r="G234" s="5" t="n">
-        <v>-1.223863</v>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>1.961956</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>0.360537</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -16248,15 +16200,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration property (Note 4)</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -16267,18 +16223,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G235" s="5" t="n">
-        <v>0.258845</v>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>-12.938121</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>-4.456872</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -16299,12 +16253,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Other comprehensive loss, net of tax</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery</t>
+          <t>Currency translation adjustments</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -16313,21 +16267,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F236" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G236" s="5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>-0.676871</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>-0.015101</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -16348,37 +16302,39 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Other comprehensive loss, net of tax</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Gain on debt forgiveness (Note 13 and 14)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" s="5" t="n">
-        <v>0.113438</v>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H237" s="5" t="n">
+        <v>-13.614992</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>-4.471973</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -16399,37 +16355,39 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Other comprehensive loss, net of tax</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E238" s="5" t="n">
-        <v>-0.475582</v>
-      </c>
-      <c r="F238" s="5" t="n">
-        <v>-0.904336</v>
-      </c>
-      <c r="G238" s="5" t="n">
-        <v>-1.304631</v>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>-1.7e-07</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -16450,37 +16408,39 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Administrative Expenses</t>
+          <t>Other comprehensive loss, net of tax</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E239" s="5" t="n">
-        <v>4.8e-08</v>
-      </c>
-      <c r="F239" s="5" t="n">
-        <v>-1.8e-07</v>
-      </c>
-      <c r="G239" s="5" t="n">
-        <v>-1.5e-07</v>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>76.123304</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>101.447812</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -16506,20 +16466,26 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted*</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" s="5" t="n">
-        <v>5.057443</v>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>8.558331000000001</v>
+        <v>-0.009727</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -16555,22 +16521,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="n">
+        <v>0.1065</v>
       </c>
       <c r="F241" s="5" t="n">
-        <v>0.112776</v>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.327995</v>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>0.303614</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -16606,22 +16572,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Gain on debt forgiveness (Note 11 and 12)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="n">
+        <v>0.001523</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.113438</v>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.080274</v>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>0.072243</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -16657,20 +16623,26 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" s="5" t="n">
-        <v>9.823529000000001</v>
-      </c>
-      <c r="F243" s="5" t="n">
-        <v>30.344658</v>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation (Note 9)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="n">
+        <v>0.047931</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -16706,20 +16678,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Total - 150,000 (475,582) (325,582) 3,270,000 245,000 (475,000) 20,000 12,000 (129,177) (177,400) 112,776 4,183 -</t>
+          <t>Part XII.6 tax</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
-      <c r="E244" s="5" t="n">
-        <v>1.652464</v>
-      </c>
-      <c r="F244" s="5" t="n">
-        <v>-0.904336</v>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="n">
+        <v>0.004364</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -16755,20 +16729,20 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Deficit - - (475,582) (475,582) - - - - - - - - - -</t>
+          <t>Share-based payments (Note 14)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" s="5" t="n">
-        <v>-1.379918</v>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F245" s="5" t="n">
-        <v>-0.904336</v>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.112776</v>
+      </c>
+      <c r="G245" s="5" t="n">
+        <v>0.16208</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -16804,12 +16778,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Administrative Expenses total</t>
+          <t>Interest expense (Note 11)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -16822,10 +16796,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G246" s="5" t="n">
+        <v>0.006181</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -16861,15 +16833,15 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Equity 4,183in Dollars) Warrants</t>
+          <t>Interest on related party loans</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" s="5" t="n">
-        <v>0.126962</v>
+        <v>0.002973</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>0.122779</v>
+        <v>0.005466</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -16905,25 +16877,25 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>Administrative Expenses</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>an are Amount 150,000 150,000 3,270,000 245,000 (475,000) 20,000 12,000 (129,177) (177,400)</t>
+          <t>Shareholder information</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" s="5" t="n">
-        <v>2.792644</v>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.122779</v>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07061000000000001</v>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>0.04427</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -16954,42 +16926,895 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Investor relations and travel</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>0.024584</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>0.083657</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Total Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="n">
+        <v>-0.110996</v>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>-0.621705</v>
+      </c>
+      <c r="G250" s="5" t="n">
+        <v>-0.7146130000000001</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (Note 4)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" s="5" t="n">
+        <v>-0.364586</v>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>-0.496069</v>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>-1.223863</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Gain on sale of exploration property (Note 4)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" s="5" t="n">
+        <v>0.258845</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Flow-through share premium recovery</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G253" s="5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Gain on debt forgiveness (Note 13 and 14)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.113438</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>-0.475582</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>-0.904336</v>
+      </c>
+      <c r="G255" s="5" t="n">
+        <v>-1.304631</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>4.8e-08</v>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>-1.8e-07</v>
+      </c>
+      <c r="G256" s="5" t="n">
+        <v>-1.5e-07</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding – basic and diluted*</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>5.057443</v>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>8.558331000000001</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>0.112776</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Gain on debt forgiveness (Note 11 and 12)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>0.113438</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
+        <v>9.823529000000001</v>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>30.344658</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Total - 150,000 (475,582) (325,582) 3,270,000 245,000 (475,000) 20,000 12,000 (129,177) (177,400) 112,776 4,183 -</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="5" t="n">
+        <v>1.652464</v>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>-0.904336</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Deficit - - (475,582) (475,582) - - - - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="5" t="n">
+        <v>-1.379918</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>-0.904336</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Administrative Expenses total</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Equity 4,183in Dollars) Warrants</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="5" t="n">
+        <v>0.126962</v>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>0.122779</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>an are Amount 150,000 150,000 3,270,000 245,000 (475,000) 20,000 12,000 (129,177) (177,400)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" s="5" t="n">
+        <v>2.792644</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>-0.122779</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
           <t>notes             $     $                       $                                      Stock</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>- - - - - - - - Capital of accompanying shares 200,000 100,000 The Number 15,000,000 15,000,000 31,150,000</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" s="5" t="n">
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" s="5" t="n">
         <v>51.35</v>
       </c>
-      <c r="F249" s="5" t="n">
+      <c r="F266" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
